--- a/financeiro/2026-07/contas-pagas.xlsx
+++ b/financeiro/2026-07/contas-pagas.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Contas Pagas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,141 +451,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Despesas com pessoal</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2100</v>
+        <v>4140.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Despesas comerciais</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>118.62</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Material de escritório</t>
+          <t>Impostos</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>456.12</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Serviços contábeis</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1058.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Serviços de terceiros</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>891.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Telefone</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Despesas com pessoal</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4140.47</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Pró-labore</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Vale transporte</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>140.47</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fretes e seguros</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1131.1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Propaganda e publicidade</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1057.9</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Impostos</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
         <v>11726.54</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Total R$</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>77386.75</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro/2026-07/contas-pagas.xlsx
+++ b/financeiro/2026-07/contas-pagas.xlsx
@@ -471,11 +471,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Impostos</t>
+          <t>Impostos (sem DIFAL)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11726.54</v>
+        <v>6040.930000000001</v>
       </c>
     </row>
   </sheetData>

--- a/financeiro/2026-07/contas-pagas.xlsx
+++ b/financeiro/2026-07/contas-pagas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,11 +471,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Impostos (sem DIFAL)</t>
+          <t>Impostos</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>6040.930000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DIFAL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5685.61</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Transferências</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3390.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Compras de fornecedores</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>48820.78</v>
       </c>
     </row>
   </sheetData>
